--- a/artfynd/A 31450-2025 artfynd.xlsx
+++ b/artfynd/A 31450-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85412549</v>
+        <v>85420013</v>
       </c>
       <c r="B2" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hällesjö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556581.8129376064</v>
+        <v>556733</v>
       </c>
       <c r="R2" t="n">
-        <v>6974290.916702046</v>
+        <v>6974272</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stöttes österut in i björkskogen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85412550</v>
+        <v>85420014</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hällesjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556597.8566580521</v>
+        <v>556722</v>
       </c>
       <c r="R3" t="n">
-        <v>6974313.999824558</v>
+        <v>6974283</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stöttes norrut</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85412551</v>
+        <v>85420015</v>
       </c>
       <c r="B4" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,31 +920,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -948,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556630.9695101039</v>
+        <v>556667</v>
       </c>
       <c r="R4" t="n">
-        <v>6974300.88950877</v>
+        <v>6974225</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,6 +1018,306 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>85412549</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>556582</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6974291</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>85412550</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556598</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6974314</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>85412551</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>556631</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6974301</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31450-2025 artfynd.xlsx
+++ b/artfynd/A 31450-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85420013</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85420014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85420015</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85412549</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85412550</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,8 +1348,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85412551</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>